--- a/products/str-tracker/Short-Term-Rental-Tracker.xlsx
+++ b/products/str-tracker/Short-Term-Rental-Tracker.xlsx
@@ -793,7 +793,7 @@
     <row r="14" ht="34" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>•  Duplicate the file per tax year (e.g. 'STR Tracker 2026').</t>
+          <t>•  Duplicate the file per tax year (e.g. 'Short-Term Rental 2026').</t>
         </is>
       </c>
     </row>
@@ -812,9 +812,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
